--- a/tables/datas/common/#Buff-Buff表.xlsx
+++ b/tables/datas/common/#Buff-Buff表.xlsx
@@ -122,6 +122,35 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>System</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Buff 类型（common.EBuffType 枚举）
+Buff = 增益效果
+Debuff = 减益效果</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>叠加规则
+Refresh = 刷新持续时间</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>脱战时是否清除
+true = 战斗结束自动清除</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -501,7 +530,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>common.EBuffType</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -568,7 +597,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Buff/Debuff</t>
+          <t>Buff类型</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1121,5 +1150,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>